--- a/INSTANCES/instances_xlsx/A_MTN_5/262FL_10A_3.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_5/262FL_10A_3.xlsx
@@ -8603,7 +8603,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -8654,7 +8654,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -8671,7 +8671,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -8739,7 +8739,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -8756,7 +8756,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>1</v>
